--- a/education_forms/034_student_leadership_project_funding_request_form--education_forms.xlsx
+++ b/education_forms/034_student_leadership_project_funding_request_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,8 +442,8 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -645,7 +645,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>School Year: e.g., 2024-2025</t>
+          <t>School Year - e.g., 2024-2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Upload File</t>
+          <t>Student Leadership Project Funding Request Form 23</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Upload File</t>
+          <t>Student Leadership Project Funding Request Form 24</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Upload File</t>
+          <t>Student Leadership Project Funding Request Form 25</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
